--- a/artfynd/A 32364-2025 artfynd.xlsx
+++ b/artfynd/A 32364-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117490684</v>
+        <v>117490682</v>
       </c>
       <c r="B2" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608195</v>
+        <v>608217</v>
       </c>
       <c r="R2" t="n">
-        <v>6968186</v>
+        <v>6968159</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117490682</v>
+        <v>117490680</v>
       </c>
       <c r="B3" t="n">
-        <v>86818</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608217</v>
+        <v>608229</v>
       </c>
       <c r="R3" t="n">
-        <v>6968159</v>
+        <v>6968013</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,12 +880,7 @@
         <v>117490681</v>
       </c>
       <c r="B4" t="n">
-        <v>82261</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,6 +971,107 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117490684</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vialamptjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608195</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6968186</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 32364-2025 artfynd.xlsx
+++ b/artfynd/A 32364-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490682</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490680</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490681</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490684</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>